--- a/results/Int Task Remove ACC -0.9/Linea_fi_explain.xlsx
+++ b/results/Int Task Remove ACC -0.9/Linea_fi_explain.xlsx
@@ -1157,7 +1157,7 @@
         <v>0.005872884982739624</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03037449593058062</v>
+        <v>0.03036524461366218</v>
       </c>
       <c r="F3" t="n">
         <v>0.002184021847673482</v>
@@ -1166,28 +1166,28 @@
         <v>0.02170738218569015</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.00150932915830912</v>
+        <v>-0.001515277998285324</v>
       </c>
       <c r="I3" t="n">
-        <v>9.406787898335379e-05</v>
+        <v>9.405738756074756e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04463495266929949</v>
+        <v>0.0446318325444945</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02370123192096927</v>
+        <v>0.02369827246550908</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02369827246550908</v>
+        <v>0.02369521623079025</v>
       </c>
       <c r="M3" t="n">
         <v>0.01620193060290426</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04006710725122923</v>
+        <v>0.04007302891554389</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02040440300293365</v>
+        <v>0.02041066868993073</v>
       </c>
       <c r="P3" t="n">
         <v>0.00727366524777433</v>
@@ -1208,7 +1208,7 @@
         <v>0.1195994144672543</v>
       </c>
       <c r="V3" t="n">
-        <v>9.406787898335379e-05</v>
+        <v>9.704229897145589e-05</v>
       </c>
       <c r="W3" t="n">
         <v>0.009002547139726124</v>
@@ -1223,7 +1223,7 @@
         <v>0.002661589083606499</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.03470530660855772</v>
+        <v>0.03470826606401791</v>
       </c>
       <c r="AB3" t="n">
         <v>0.001387737771559038</v>
@@ -1301,7 +1301,7 @@
         <v>0.01125657654009167</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.006661939250533579</v>
+        <v>0.00666491367052168</v>
       </c>
       <c r="BB3" t="n">
         <v>0.006481908720889201</v>
@@ -1316,10 +1316,10 @@
         <v>-0.0009030771756960675</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.01421647633585122</v>
+        <v>0.01421942358017777</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.004759592890526729</v>
+        <v>0.004756638680777837</v>
       </c>
       <c r="BH3" t="n">
         <v>0.0003456636822469416</v>
@@ -1340,7 +1340,7 @@
         <v>0.02622094197166485</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.006668047484373138</v>
+        <v>0.00666491367052168</v>
       </c>
       <c r="BO3" t="n">
         <v>0.02026641669076991</v>
@@ -1355,7 +1355,7 @@
         <v>0.00275127113752375</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.002088539989375286</v>
+        <v>0.002091660114180279</v>
       </c>
       <c r="BT3" t="n">
         <v>0.001327178921898735</v>
@@ -1367,7 +1367,7 @@
         <v>0.004557046064061585</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.008279933859219038</v>
+        <v>0.008282814873336005</v>
       </c>
       <c r="BX3" t="n">
         <v>-9.995999787123068e-05</v>
@@ -1385,7 +1385,7 @@
         <v>0.0008728987040084535</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.002030676071023038</v>
+        <v>0.002033623315349592</v>
       </c>
       <c r="CD3" t="n">
         <v>-0.0005948769398728627</v>
@@ -1406,7 +1406,7 @@
         <v>0.02972716091720777</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.008282814873336005</v>
+        <v>0.008279933859219038</v>
       </c>
       <c r="CK3" t="n">
         <v>0.007945659719451064</v>
@@ -1428,7 +1428,7 @@
         <v>0.01145012447400461</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03270926980053723</v>
+        <v>0.03268921388654578</v>
       </c>
       <c r="F4" t="n">
         <v>0.002920908574377343</v>
@@ -1437,28 +1437,28 @@
         <v>0.05468928294964336</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002936356107886548</v>
+        <v>0.002935629981215447</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001070711668480681</v>
+        <v>0.001073075757025371</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04428297753759203</v>
+        <v>0.04427809925961074</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01291511426569985</v>
+        <v>0.01292209968582649</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01292209968582649</v>
+        <v>0.01292452383317492</v>
       </c>
       <c r="M4" t="n">
         <v>0.03239192947161385</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04062984032754178</v>
+        <v>0.04063619503031831</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02974204218955126</v>
+        <v>0.02976092186131991</v>
       </c>
       <c r="P4" t="n">
         <v>0.01821371798657882</v>
@@ -1479,7 +1479,7 @@
         <v>0.05451432125979587</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001070711668480681</v>
+        <v>0.001073030794171756</v>
       </c>
       <c r="W4" t="n">
         <v>0.02960615851271703</v>
@@ -1494,7 +1494,7 @@
         <v>0.01305070478122668</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03088892562141527</v>
+        <v>0.03088835776433968</v>
       </c>
       <c r="AB4" t="n">
         <v>0.002761503144583464</v>
@@ -1572,7 +1572,7 @@
         <v>0.02812195219494185</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.008704350194535184</v>
+        <v>0.008704581431167679</v>
       </c>
       <c r="BB4" t="n">
         <v>0.0147795718627242</v>
@@ -1587,10 +1587,10 @@
         <v>0.003854980884221728</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.02480069184406648</v>
+        <v>0.02479461278151418</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.02423814092343936</v>
+        <v>0.02423991543767897</v>
       </c>
       <c r="BH4" t="n">
         <v>0.000935505780414492</v>
@@ -1611,7 +1611,7 @@
         <v>0.02702221192345177</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.008711996682953943</v>
+        <v>0.008704581431167679</v>
       </c>
       <c r="BO4" t="n">
         <v>0.02742626468394797</v>
@@ -1626,7 +1626,7 @@
         <v>0.01177200767368808</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.0130947391344969</v>
+        <v>0.01309437990082745</v>
       </c>
       <c r="BT4" t="n">
         <v>0.002375221859880209</v>
@@ -1638,7 +1638,7 @@
         <v>0.01937947570181254</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0261320507024158</v>
+        <v>0.02613627851621273</v>
       </c>
       <c r="BX4" t="n">
         <v>0.000181440443438089</v>
@@ -1656,7 +1656,7 @@
         <v>0.002169735804199412</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.01252959351135891</v>
+        <v>0.01252265553119706</v>
       </c>
       <c r="CD4" t="n">
         <v>0.004499814999036689</v>
@@ -1677,7 +1677,7 @@
         <v>0.03421238728413903</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.02613627851621273</v>
+        <v>0.0261320507024158</v>
       </c>
       <c r="CK4" t="n">
         <v>0.007317152099463472</v>
@@ -1717,7 +1717,7 @@
         <v>-0.01060513447432767</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.003728913879846107</v>
+        <v>-0.00375850843444806</v>
       </c>
       <c r="L5" t="n">
         <v>-0.00375850843444806</v>
@@ -1858,7 +1858,7 @@
         <v>-0.01032143910350933</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.0318302387267904</v>
+        <v>-0.03180076628352486</v>
       </c>
       <c r="BG5" t="n">
         <v>-0.02189802534630115</v>
@@ -1927,7 +1927,7 @@
         <v>-0.001827291482463866</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.02452107279693483</v>
+        <v>-0.02449160035366928</v>
       </c>
       <c r="CD5" t="n">
         <v>-0.007644259369423001</v>
@@ -1970,7 +1970,7 @@
         <v>0.0003385191587438885</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0113970635434559</v>
+        <v>0.01141179976508867</v>
       </c>
       <c r="F6" t="n">
         <v>0.0002170773724869706</v>
@@ -1982,7 +1982,7 @@
         <v>-0.003032696020484479</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0003933375892087698</v>
+        <v>-0.0004377294211116989</v>
       </c>
       <c r="J6" t="n">
         <v>0.01509267494420046</v>
@@ -1997,7 +1997,7 @@
         <v>-0.003645962159384408</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01868160838423417</v>
+        <v>0.01870371271668332</v>
       </c>
       <c r="O6" t="n">
         <v>0.003122044731798476</v>
@@ -2036,7 +2036,7 @@
         <v>-0.005342995742301584</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01523069622563455</v>
+        <v>0.01523809486428504</v>
       </c>
       <c r="AB6" t="n">
         <v>0.0004069974037743535</v>
@@ -2168,7 +2168,7 @@
         <v>-0.002440008516249531</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.0008699820714739487</v>
+        <v>0.0008933830075113947</v>
       </c>
       <c r="BT6" t="n">
         <v>-0.000100833864665606</v>
@@ -2241,7 +2241,7 @@
         <v>0.006716190707604358</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01814876201536169</v>
+        <v>0.0181635069283667</v>
       </c>
       <c r="F7" t="n">
         <v>0.001372902557349798</v>
@@ -2250,10 +2250,10 @@
         <v>0.00519781990208556</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0008550730223743586</v>
+        <v>-0.0008848172222553796</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0001180899827373572</v>
+        <v>-8.85478852484356e-05</v>
       </c>
       <c r="J7" t="n">
         <v>0.02799200438493657</v>
@@ -2271,7 +2271,7 @@
         <v>0.03123829391120031</v>
       </c>
       <c r="O7" t="n">
-        <v>0.008986264362133279</v>
+        <v>0.008971519449128263</v>
       </c>
       <c r="P7" t="n">
         <v>0.005283512854357153</v>
@@ -2512,7 +2512,7 @@
         <v>0.009667835795490395</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04053367460301624</v>
+        <v>0.04048926962965924</v>
       </c>
       <c r="F8" t="n">
         <v>0.00441173768307066</v>
@@ -2542,7 +2542,7 @@
         <v>0.04746392079923327</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02283809540458538</v>
+        <v>0.02286040355449614</v>
       </c>
       <c r="P8" t="n">
         <v>0.01693098670221116</v>
@@ -2563,7 +2563,7 @@
         <v>0.1507046894235935</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0006966535504257077</v>
+        <v>0.0007189617003364734</v>
       </c>
       <c r="W8" t="n">
         <v>0.03109551075958515</v>
@@ -2656,7 +2656,7 @@
         <v>0.0230344338595465</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.01070033783730476</v>
+        <v>0.01070777388727502</v>
       </c>
       <c r="BB8" t="n">
         <v>0.01513244300135459</v>
@@ -2783,7 +2783,7 @@
         <v>0.02507051081165781</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09289113622843544</v>
+        <v>0.09286139202855441</v>
       </c>
       <c r="F9" t="n">
         <v>0.007296898079763625</v>
@@ -2810,10 +2810,10 @@
         <v>0.0667256115531978</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1413741820345033</v>
+        <v>0.1414039262343843</v>
       </c>
       <c r="O9" t="n">
-        <v>0.09419656786271453</v>
+        <v>0.09425897035881436</v>
       </c>
       <c r="P9" t="n">
         <v>0.04489859594383776</v>
@@ -2966,7 +2966,7 @@
         <v>0.05828291558628642</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.02522720150423065</v>
+        <v>0.02519586336571609</v>
       </c>
       <c r="BO9" t="n">
         <v>0.0738130345030964</v>
@@ -2993,7 +2993,7 @@
         <v>0.04026950799122533</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.04278305963699228</v>
+        <v>0.04281186977816197</v>
       </c>
       <c r="BX9" t="n">
         <v>5.89448865311093e-05</v>
@@ -3032,7 +3032,7 @@
         <v>0.0759369422962522</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.04281186977816197</v>
+        <v>0.04278305963699228</v>
       </c>
       <c r="CK9" t="n">
         <v>0.02061273051754904</v>
